--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/33.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/33.xlsx
@@ -426,13 +426,13 @@
         <v>-7.77947730913816</v>
       </c>
       <c r="E2">
-        <v>-9.784381514270445</v>
+        <v>-9.745943826893338</v>
       </c>
       <c r="F2">
-        <v>-5.554711372236109</v>
+        <v>-4.651413996016374</v>
       </c>
       <c r="G2">
-        <v>-11.45192304375371</v>
+        <v>-11.42862673479385</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.481756593144844</v>
       </c>
       <c r="E3">
-        <v>-9.479547286444115</v>
+        <v>-10.12186151121807</v>
       </c>
       <c r="F3">
-        <v>-5.520561097688296</v>
+        <v>-4.927301759518749</v>
       </c>
       <c r="G3">
-        <v>-11.07123348055629</v>
+        <v>-10.33799730179082</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.230513053008269</v>
       </c>
       <c r="E4">
-        <v>-9.724813967173549</v>
+        <v>-10.03055841827542</v>
       </c>
       <c r="F4">
-        <v>-5.478253060957715</v>
+        <v>-4.963997607095365</v>
       </c>
       <c r="G4">
-        <v>-11.57831636189754</v>
+        <v>-10.70048879615885</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.045735201936539</v>
       </c>
       <c r="E5">
-        <v>-10.30055509556074</v>
+        <v>-11.1067593231463</v>
       </c>
       <c r="F5">
-        <v>-5.520194130928856</v>
+        <v>-5.055224880798272</v>
       </c>
       <c r="G5">
-        <v>-11.19333633168123</v>
+        <v>-10.80798883091007</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.902615190510284</v>
       </c>
       <c r="E6">
-        <v>-10.93455051358261</v>
+        <v>-11.9789388885496</v>
       </c>
       <c r="F6">
-        <v>-4.947965384381583</v>
+        <v>-4.274334527322817</v>
       </c>
       <c r="G6">
-        <v>-11.59158833896448</v>
+        <v>-10.64923493011986</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.79767722563551</v>
       </c>
       <c r="E7">
-        <v>-12.38894239673007</v>
+        <v>-11.66468996326132</v>
       </c>
       <c r="F7">
-        <v>-4.911482427227488</v>
+        <v>-4.647413809828255</v>
       </c>
       <c r="G7">
-        <v>-10.68639911434371</v>
+        <v>-11.09267919455969</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.719466822490352</v>
       </c>
       <c r="E8">
-        <v>-11.6890033402085</v>
+        <v>-11.77970414610813</v>
       </c>
       <c r="F8">
-        <v>-5.396435212583207</v>
+        <v>-4.6930841898468</v>
       </c>
       <c r="G8">
-        <v>-11.1806966688123</v>
+        <v>-11.05664059581919</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.651486325471351</v>
       </c>
       <c r="E9">
-        <v>-12.57163915209552</v>
+        <v>-13.31623349080672</v>
       </c>
       <c r="F9">
-        <v>-4.630878768100974</v>
+        <v>-4.532124119808828</v>
       </c>
       <c r="G9">
-        <v>-10.46798256184476</v>
+        <v>-10.25170793230971</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.581677397674143</v>
       </c>
       <c r="E10">
-        <v>-12.41877145501859</v>
+        <v>-13.14558247630167</v>
       </c>
       <c r="F10">
-        <v>-4.99176613917201</v>
+        <v>-3.99448136906324</v>
       </c>
       <c r="G10">
-        <v>-10.29059360021399</v>
+        <v>-10.59821942335969</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.508251303669788</v>
       </c>
       <c r="E11">
-        <v>-13.53848646662917</v>
+        <v>-14.1366842976204</v>
       </c>
       <c r="F11">
-        <v>-4.487263883110221</v>
+        <v>-3.956530544871383</v>
       </c>
       <c r="G11">
-        <v>-9.852879890102633</v>
+        <v>-10.72536754588648</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.421892427050668</v>
       </c>
       <c r="E12">
-        <v>-13.71368406903792</v>
+        <v>-14.85732753730503</v>
       </c>
       <c r="F12">
-        <v>-3.958245265395179</v>
+        <v>-3.491182730837719</v>
       </c>
       <c r="G12">
-        <v>-10.13062472921087</v>
+        <v>-10.69170591884317</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.312776220102665</v>
       </c>
       <c r="E13">
-        <v>-14.23051427905933</v>
+        <v>-15.33813373659543</v>
       </c>
       <c r="F13">
-        <v>-3.719853552380523</v>
+        <v>-3.140919171707587</v>
       </c>
       <c r="G13">
-        <v>-10.18637431609219</v>
+        <v>-9.527585685413847</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.187608504854816</v>
       </c>
       <c r="E14">
-        <v>-14.95961217971628</v>
+        <v>-15.91454507913575</v>
       </c>
       <c r="F14">
-        <v>-4.100738540922541</v>
+        <v>-2.898540526383258</v>
       </c>
       <c r="G14">
-        <v>-10.05776293243705</v>
+        <v>-9.787076176418541</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.045164801518823</v>
       </c>
       <c r="E15">
-        <v>-16.72328978063961</v>
+        <v>-16.17371417506873</v>
       </c>
       <c r="F15">
-        <v>-2.868561910075944</v>
+        <v>-2.830913439986109</v>
       </c>
       <c r="G15">
-        <v>-10.05244288575544</v>
+        <v>-9.327863783575156</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.88144879800792</v>
       </c>
       <c r="E16">
-        <v>-18.1449906099257</v>
+        <v>-17.51706334707411</v>
       </c>
       <c r="F16">
-        <v>-3.442806074514228</v>
+        <v>-2.54986991776871</v>
       </c>
       <c r="G16">
-        <v>-9.621303919085074</v>
+        <v>-9.015378079577809</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.709103561372017</v>
       </c>
       <c r="E17">
-        <v>-17.67680073922067</v>
+        <v>-17.81990051786306</v>
       </c>
       <c r="F17">
-        <v>-2.932512701939468</v>
+        <v>-2.690399134184034</v>
       </c>
       <c r="G17">
-        <v>-9.921689579136386</v>
+        <v>-8.766431676115694</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.538097965147694</v>
       </c>
       <c r="E18">
-        <v>-17.40367488639605</v>
+        <v>-17.92105304177239</v>
       </c>
       <c r="F18">
-        <v>-2.397141334612356</v>
+        <v>-2.231685714679391</v>
       </c>
       <c r="G18">
-        <v>-8.948726866235662</v>
+        <v>-8.843024457712271</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.371999883841936</v>
       </c>
       <c r="E19">
-        <v>-20.78176705647589</v>
+        <v>-19.48810430128267</v>
       </c>
       <c r="F19">
-        <v>-2.114330904724786</v>
+        <v>-1.90234505940917</v>
       </c>
       <c r="G19">
-        <v>-8.107662908710582</v>
+        <v>-7.694324745404877</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.223365447497078</v>
       </c>
       <c r="E20">
-        <v>-20.39953667938446</v>
+        <v>-20.67064736127567</v>
       </c>
       <c r="F20">
-        <v>-2.027180855378458</v>
+        <v>-1.612611963136403</v>
       </c>
       <c r="G20">
-        <v>-8.221095441068169</v>
+        <v>-7.759989416176321</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.100640795615962</v>
       </c>
       <c r="E21">
-        <v>-21.29804479266836</v>
+        <v>-21.08611220910939</v>
       </c>
       <c r="F21">
-        <v>-1.291993188250258</v>
+        <v>-1.310152658454428</v>
       </c>
       <c r="G21">
-        <v>-7.58429545386166</v>
+        <v>-7.119369059417493</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.000477862465281</v>
       </c>
       <c r="E22">
-        <v>-21.2524928726252</v>
+        <v>-20.65958882774894</v>
       </c>
       <c r="F22">
-        <v>-1.477848183844563</v>
+        <v>-1.308474386096356</v>
       </c>
       <c r="G22">
-        <v>-7.948968597740078</v>
+        <v>-7.617198965976476</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.918424380106191</v>
       </c>
       <c r="E23">
-        <v>-22.01512412330895</v>
+        <v>-22.63070223754162</v>
       </c>
       <c r="F23">
-        <v>-1.365533161168589</v>
+        <v>-0.9111040578712252</v>
       </c>
       <c r="G23">
-        <v>-7.68377072622568</v>
+        <v>-7.4017817677361</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.852753843071848</v>
       </c>
       <c r="E24">
-        <v>-22.5332766477406</v>
+        <v>-22.45824889038152</v>
       </c>
       <c r="F24">
-        <v>-1.266352732031404</v>
+        <v>-0.4593795741440016</v>
       </c>
       <c r="G24">
-        <v>-7.406618474768975</v>
+        <v>-6.654439354427787</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.793066398247199</v>
       </c>
       <c r="E25">
-        <v>-22.71302083805305</v>
+        <v>-23.03186616445912</v>
       </c>
       <c r="F25">
-        <v>-0.8484173546643726</v>
+        <v>-0.7445740454168294</v>
       </c>
       <c r="G25">
-        <v>-7.044825505509723</v>
+        <v>-7.073196880781278</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.726177346043205</v>
       </c>
       <c r="E26">
-        <v>-23.3658954642129</v>
+        <v>-22.41522838730865</v>
       </c>
       <c r="F26">
-        <v>-0.9425414291748693</v>
+        <v>-0.4303751179023797</v>
       </c>
       <c r="G26">
-        <v>-7.624641072348758</v>
+        <v>-6.500081858113728</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.650725145186685</v>
       </c>
       <c r="E27">
-        <v>-22.35829641208422</v>
+        <v>-23.27420292250559</v>
       </c>
       <c r="F27">
-        <v>-0.8610043973499111</v>
+        <v>-0.5268302182843542</v>
       </c>
       <c r="G27">
-        <v>-7.930595069997122</v>
+        <v>-6.861801995371116</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.559683764521903</v>
       </c>
       <c r="E28">
-        <v>-23.50490603082635</v>
+        <v>-23.07598708671585</v>
       </c>
       <c r="F28">
-        <v>-0.7636819962972056</v>
+        <v>-0.5396028152681197</v>
       </c>
       <c r="G28">
-        <v>-7.642147237160424</v>
+        <v>-6.528287706108319</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.444035045547851</v>
       </c>
       <c r="E29">
-        <v>-22.86877317307287</v>
+        <v>-23.48735819404663</v>
       </c>
       <c r="F29">
-        <v>-0.8576056058962247</v>
+        <v>-0.2023968115083166</v>
       </c>
       <c r="G29">
-        <v>-7.539252171254336</v>
+        <v>-6.841902306134557</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.306166649027265</v>
       </c>
       <c r="E30">
-        <v>-24.44900682041948</v>
+        <v>-23.18894987083718</v>
       </c>
       <c r="F30">
-        <v>-0.8243135199777126</v>
+        <v>-0.4099765706084419</v>
       </c>
       <c r="G30">
-        <v>-7.46078893142807</v>
+        <v>-6.340487078756543</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.14670747190825</v>
       </c>
       <c r="E31">
-        <v>-22.42530424197572</v>
+        <v>-22.87008190206108</v>
       </c>
       <c r="F31">
-        <v>-0.9131161622926252</v>
+        <v>-0.5440329241382915</v>
       </c>
       <c r="G31">
-        <v>-7.515403001189426</v>
+        <v>-6.501141232686295</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.963377212014827</v>
       </c>
       <c r="E32">
-        <v>-22.20805070145773</v>
+        <v>-23.14903590093358</v>
       </c>
       <c r="F32">
-        <v>-1.075521733448482</v>
+        <v>-0.8181943699732326</v>
       </c>
       <c r="G32">
-        <v>-7.643372139009954</v>
+        <v>-6.255233910029231</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.762194711779415</v>
       </c>
       <c r="E33">
-        <v>-22.78065359735761</v>
+        <v>-21.78607843647499</v>
       </c>
       <c r="F33">
-        <v>-0.7531865813037358</v>
+        <v>-0.6072257598282546</v>
       </c>
       <c r="G33">
-        <v>-6.620287766644665</v>
+        <v>-6.205747875308206</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.551559395567391</v>
       </c>
       <c r="E34">
-        <v>-21.92370781851611</v>
+        <v>-21.93139263890713</v>
       </c>
       <c r="F34">
-        <v>-1.293077521180522</v>
+        <v>-0.9156020928684265</v>
       </c>
       <c r="G34">
-        <v>-6.805691559026009</v>
+        <v>-6.055161090363377</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.336560151083674</v>
       </c>
       <c r="E35">
-        <v>-22.81603909325355</v>
+        <v>-21.33026941370694</v>
       </c>
       <c r="F35">
-        <v>-1.058356304127671</v>
+        <v>-1.057425219166924</v>
       </c>
       <c r="G35">
-        <v>-7.538338460685497</v>
+        <v>-6.348107954587945</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.12364518146126</v>
       </c>
       <c r="E36">
-        <v>-21.5588441392441</v>
+        <v>-21.26777647240109</v>
       </c>
       <c r="F36">
-        <v>-1.368488776061778</v>
+        <v>-0.7931900999197296</v>
       </c>
       <c r="G36">
-        <v>-6.843590684359585</v>
+        <v>-5.302727058015664</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.923144607064935</v>
       </c>
       <c r="E37">
-        <v>-20.51503540895009</v>
+        <v>-20.23222767869707</v>
       </c>
       <c r="F37">
-        <v>-0.8969182660982836</v>
+        <v>-0.9688777140120739</v>
       </c>
       <c r="G37">
-        <v>-6.977687641973304</v>
+        <v>-6.428203293365073</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.73931066820827</v>
       </c>
       <c r="E38">
-        <v>-20.82928433423837</v>
+        <v>-19.80780550927618</v>
       </c>
       <c r="F38">
-        <v>-1.388599879866944</v>
+        <v>-1.172191380987782</v>
       </c>
       <c r="G38">
-        <v>-6.057988296253915</v>
+        <v>-6.506123603722898</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.572768447774118</v>
       </c>
       <c r="E39">
-        <v>-20.09701650177605</v>
+        <v>-20.02066643000673</v>
       </c>
       <c r="F39">
-        <v>-1.240012305357186</v>
+        <v>-1.166759775927625</v>
       </c>
       <c r="G39">
-        <v>-7.009687375155899</v>
+        <v>-5.777389766890829</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.431021056413196</v>
       </c>
       <c r="E40">
-        <v>-19.10600524993747</v>
+        <v>-19.51193765998504</v>
       </c>
       <c r="F40">
-        <v>-1.321384492068987</v>
+        <v>-1.428937230546266</v>
       </c>
       <c r="G40">
-        <v>-6.621499426312038</v>
+        <v>-6.31983258513703</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.315215494245291</v>
       </c>
       <c r="E41">
-        <v>-19.35749405395344</v>
+        <v>-19.34959186681006</v>
       </c>
       <c r="F41">
-        <v>-1.856621663876845</v>
+        <v>-0.9629242374881538</v>
       </c>
       <c r="G41">
-        <v>-6.116671026483036</v>
+        <v>-6.003804597412663</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.221839980771731</v>
       </c>
       <c r="E42">
-        <v>-17.67044729018791</v>
+        <v>-17.82325611710274</v>
       </c>
       <c r="F42">
-        <v>-1.451477935943843</v>
+        <v>-1.027534409804307</v>
       </c>
       <c r="G42">
-        <v>-6.539020494746636</v>
+        <v>-5.847358146863325</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.153042330812054</v>
       </c>
       <c r="E43">
-        <v>-17.33676215445871</v>
+        <v>-18.3058737059962</v>
       </c>
       <c r="F43">
-        <v>-1.430065466948879</v>
+        <v>-1.110546763973651</v>
       </c>
       <c r="G43">
-        <v>-7.280778017730199</v>
+        <v>-5.977091805456284</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.107288117848437</v>
       </c>
       <c r="E44">
-        <v>-18.27831794165953</v>
+        <v>-16.94576918016245</v>
       </c>
       <c r="F44">
-        <v>-1.958354292982055</v>
+        <v>-1.113296115383543</v>
       </c>
       <c r="G44">
-        <v>-5.876441289425822</v>
+        <v>-5.724166126255965</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.078540475092901</v>
       </c>
       <c r="E45">
-        <v>-15.94719990520506</v>
+        <v>-17.04336232350175</v>
       </c>
       <c r="F45">
-        <v>-1.305091333623323</v>
+        <v>-1.010143664549934</v>
       </c>
       <c r="G45">
-        <v>-6.164534893889819</v>
+        <v>-5.918736819235551</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.064092853389606</v>
       </c>
       <c r="E46">
-        <v>-15.74643906702302</v>
+        <v>-16.07345828901292</v>
       </c>
       <c r="F46">
-        <v>-1.533922030074867</v>
+        <v>-1.348528435123921</v>
       </c>
       <c r="G46">
-        <v>-6.695880763488383</v>
+        <v>-5.298708055730989</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.061418575115661</v>
       </c>
       <c r="E47">
-        <v>-15.80730628616011</v>
+        <v>-16.2892310185304</v>
       </c>
       <c r="F47">
-        <v>-1.903136150278843</v>
+        <v>-1.29659808264242</v>
       </c>
       <c r="G47">
-        <v>-6.650152197954431</v>
+        <v>-5.205519509346045</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.06442638917528</v>
       </c>
       <c r="E48">
-        <v>-15.66257625687497</v>
+        <v>-16.16917664411305</v>
       </c>
       <c r="F48">
-        <v>-1.682166660479867</v>
+        <v>-1.355332644970516</v>
       </c>
       <c r="G48">
-        <v>-6.279473724467775</v>
+        <v>-5.016924351064843</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.068069124138365</v>
       </c>
       <c r="E49">
-        <v>-15.0759849047654</v>
+        <v>-14.91145638711872</v>
       </c>
       <c r="F49">
-        <v>-1.919582556694025</v>
+        <v>-1.177942735865419</v>
       </c>
       <c r="G49">
-        <v>-5.745264232977741</v>
+        <v>-5.750110871647234</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.07145183192328</v>
       </c>
       <c r="E50">
-        <v>-13.7386450177682</v>
+        <v>-14.65401716825666</v>
       </c>
       <c r="F50">
-        <v>-1.830079115556344</v>
+        <v>-1.586458747495217</v>
       </c>
       <c r="G50">
-        <v>-6.255075003843347</v>
+        <v>-5.524133033136582</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.071399835662832</v>
       </c>
       <c r="E51">
-        <v>-14.04557140058608</v>
+        <v>-15.22968584105974</v>
       </c>
       <c r="F51">
-        <v>-2.527523050343387</v>
+        <v>-1.420740535095565</v>
       </c>
       <c r="G51">
-        <v>-6.338153144151357</v>
+        <v>-4.413934965450911</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.065001855399685</v>
       </c>
       <c r="E52">
-        <v>-14.36725608019495</v>
+        <v>-14.2177439823577</v>
       </c>
       <c r="F52">
-        <v>-1.92804101624401</v>
+        <v>-1.943982118543484</v>
       </c>
       <c r="G52">
-        <v>-4.698996110200936</v>
+        <v>-4.739302002141562</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.0564323994927</v>
       </c>
       <c r="E53">
-        <v>-12.9673055115677</v>
+        <v>-13.41375870703591</v>
       </c>
       <c r="F53">
-        <v>-1.862778918781854</v>
+        <v>-1.652564122973423</v>
       </c>
       <c r="G53">
-        <v>-5.329463023790819</v>
+        <v>-5.081774627633627</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.048716354777252</v>
       </c>
       <c r="E54">
-        <v>-12.67082178981152</v>
+        <v>-13.62516598760999</v>
       </c>
       <c r="F54">
-        <v>-2.373439258116054</v>
+        <v>-1.482689162946523</v>
       </c>
       <c r="G54">
-        <v>-5.641809684875516</v>
+        <v>-5.360929759141591</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.043197910048748</v>
       </c>
       <c r="E55">
-        <v>-12.99266496601066</v>
+        <v>-13.62037939058388</v>
       </c>
       <c r="F55">
-        <v>-2.208583376182716</v>
+        <v>-1.748572733325289</v>
       </c>
       <c r="G55">
-        <v>-5.193700861770846</v>
+        <v>-5.368815478616136</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.047457371132259</v>
       </c>
       <c r="E56">
-        <v>-11.56419859655711</v>
+        <v>-12.7545895020054</v>
       </c>
       <c r="F56">
-        <v>-2.250388593899799</v>
+        <v>-1.594174161484892</v>
       </c>
       <c r="G56">
-        <v>-4.816040447741869</v>
+        <v>-5.041952075341734</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.06733021252075</v>
       </c>
       <c r="E57">
-        <v>-12.02715355130927</v>
+        <v>-13.6192065158159</v>
       </c>
       <c r="F57">
-        <v>-2.347939624355677</v>
+        <v>-1.667589879292804</v>
       </c>
       <c r="G57">
-        <v>-5.754553623760936</v>
+        <v>-5.439585010609136</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.103629415968747</v>
       </c>
       <c r="E58">
-        <v>-10.92848688688634</v>
+        <v>-12.1937832808955</v>
       </c>
       <c r="F58">
-        <v>-2.229745678222035</v>
+        <v>-1.76453371644243</v>
       </c>
       <c r="G58">
-        <v>-5.310228754207653</v>
+        <v>-5.160337183826072</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.15905923025996</v>
       </c>
       <c r="E59">
-        <v>-13.67109829946979</v>
+        <v>-12.24070280008898</v>
       </c>
       <c r="F59">
-        <v>-2.464044427899458</v>
+        <v>-1.580100199311328</v>
       </c>
       <c r="G59">
-        <v>-5.240316653509324</v>
+        <v>-5.929966189704759</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.235237052628624</v>
       </c>
       <c r="E60">
-        <v>-11.49894328610658</v>
+        <v>-12.01710939596025</v>
       </c>
       <c r="F60">
-        <v>-2.611527788661285</v>
+        <v>-1.927920074603201</v>
       </c>
       <c r="G60">
-        <v>-5.44065431681832</v>
+        <v>-5.405701577014695</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.328733864678584</v>
       </c>
       <c r="E61">
-        <v>-11.99289111696723</v>
+        <v>-11.98411040586636</v>
       </c>
       <c r="F61">
-        <v>-2.453080156956004</v>
+        <v>-1.699098490193089</v>
       </c>
       <c r="G61">
-        <v>-6.444941411611627</v>
+        <v>-6.01036278812596</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.435490768762989</v>
       </c>
       <c r="E62">
-        <v>-11.90241220629398</v>
+        <v>-12.0047376049713</v>
       </c>
       <c r="F62">
-        <v>-2.340509997119968</v>
+        <v>-2.133681567254182</v>
       </c>
       <c r="G62">
-        <v>-5.715270690391944</v>
+        <v>-5.649298138885348</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.554224820420226</v>
       </c>
       <c r="E63">
-        <v>-11.26046025944064</v>
+        <v>-12.47106174438516</v>
       </c>
       <c r="F63">
-        <v>-2.422114955071956</v>
+        <v>-2.029025629584492</v>
       </c>
       <c r="G63">
-        <v>-6.179326411359282</v>
+        <v>-5.354222593879028</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.67917757792039</v>
       </c>
       <c r="E64">
-        <v>-11.69181099409326</v>
+        <v>-11.62313215729293</v>
       </c>
       <c r="F64">
-        <v>-2.643251775086298</v>
+        <v>-2.420036581258332</v>
       </c>
       <c r="G64">
-        <v>-6.446417914922143</v>
+        <v>-5.370348261200818</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.801788998049874</v>
       </c>
       <c r="E65">
-        <v>-10.75020992215237</v>
+        <v>-12.18053749442307</v>
       </c>
       <c r="F65">
-        <v>-2.395083669983802</v>
+        <v>-2.300318439103539</v>
       </c>
       <c r="G65">
-        <v>-6.690471332077214</v>
+        <v>-5.890223090505808</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.919160948444695</v>
       </c>
       <c r="E66">
-        <v>-11.24525817219689</v>
+        <v>-12.04251413514328</v>
       </c>
       <c r="F66">
-        <v>-2.894871687156259</v>
+        <v>-1.898962006936136</v>
       </c>
       <c r="G66">
-        <v>-6.103220279956977</v>
+        <v>-5.348088152994759</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.025774148613513</v>
       </c>
       <c r="E67">
-        <v>-10.31566661332434</v>
+        <v>-11.86441830936962</v>
       </c>
       <c r="F67">
-        <v>-2.930693607122921</v>
+        <v>-2.179839855672976</v>
       </c>
       <c r="G67">
-        <v>-6.643044456681615</v>
+        <v>-5.755252148869721</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.113601786428906</v>
       </c>
       <c r="E68">
-        <v>-11.11664951037905</v>
+        <v>-11.08818352276683</v>
       </c>
       <c r="F68">
-        <v>-2.68898925286447</v>
+        <v>-2.243582727318398</v>
       </c>
       <c r="G68">
-        <v>-5.450678648711233</v>
+        <v>-5.653793859727678</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.18095664848216</v>
       </c>
       <c r="E69">
-        <v>-11.63796290966805</v>
+        <v>-11.93158010737738</v>
       </c>
       <c r="F69">
-        <v>-2.812657879163214</v>
+        <v>-2.450918118034697</v>
       </c>
       <c r="G69">
-        <v>-5.724722297906563</v>
+        <v>-5.545482741319343</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.225310978814374</v>
       </c>
       <c r="E70">
-        <v>-10.70462630279116</v>
+        <v>-11.51317175143868</v>
       </c>
       <c r="F70">
-        <v>-2.899330788885528</v>
+        <v>-2.199856525594223</v>
       </c>
       <c r="G70">
-        <v>-6.773076064373109</v>
+        <v>-5.299572108116739</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.241917757359956</v>
       </c>
       <c r="E71">
-        <v>-10.74914573076057</v>
+        <v>-12.40062585966986</v>
       </c>
       <c r="F71">
-        <v>-2.87349649469442</v>
+        <v>-2.440954514913825</v>
       </c>
       <c r="G71">
-        <v>-5.526241850645098</v>
+        <v>-6.295387516875052</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.229458760661423</v>
       </c>
       <c r="E72">
-        <v>-11.46066862379375</v>
+        <v>-11.38478951332123</v>
       </c>
       <c r="F72">
-        <v>-2.83200854169261</v>
+        <v>-2.40965299586424</v>
       </c>
       <c r="G72">
-        <v>-5.15511976405618</v>
+        <v>-5.200944335410772</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.187906087891672</v>
       </c>
       <c r="E73">
-        <v>-11.59265552722131</v>
+        <v>-12.64810243571503</v>
       </c>
       <c r="F73">
-        <v>-2.886612864150348</v>
+        <v>-2.638045485959703</v>
       </c>
       <c r="G73">
-        <v>-6.141596123848209</v>
+        <v>-5.050264855190844</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.115153662203522</v>
       </c>
       <c r="E74">
-        <v>-12.25379461844515</v>
+        <v>-12.14113524208233</v>
       </c>
       <c r="F74">
-        <v>-2.93886627991894</v>
+        <v>-2.540640248166718</v>
       </c>
       <c r="G74">
-        <v>-5.861166432307625</v>
+        <v>-4.815656424459313</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.009262429230841</v>
       </c>
       <c r="E75">
-        <v>-11.93933285487851</v>
+        <v>-12.72351058489076</v>
       </c>
       <c r="F75">
-        <v>-2.914160222130445</v>
+        <v>-2.585909698362308</v>
       </c>
       <c r="G75">
-        <v>-4.755808382200368</v>
+        <v>-4.985805222995695</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.871812315640581</v>
       </c>
       <c r="E76">
-        <v>-12.84236491369608</v>
+        <v>-12.72238752333686</v>
       </c>
       <c r="F76">
-        <v>-3.165935867272132</v>
+        <v>-2.53949875788566</v>
       </c>
       <c r="G76">
-        <v>-5.659958095521801</v>
+        <v>-4.532118130657353</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.702368649494537</v>
       </c>
       <c r="E77">
-        <v>-13.10202308482189</v>
+        <v>-13.10025245148489</v>
       </c>
       <c r="F77">
-        <v>-3.274933278499895</v>
+        <v>-2.863668743827607</v>
       </c>
       <c r="G77">
-        <v>-4.616129844807438</v>
+        <v>-4.700078658592277</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.500281898213554</v>
       </c>
       <c r="E78">
-        <v>-12.78805039644808</v>
+        <v>-14.26763870897421</v>
       </c>
       <c r="F78">
-        <v>-3.389152717834904</v>
+        <v>-2.962897218274154</v>
       </c>
       <c r="G78">
-        <v>-6.010465415037677</v>
+        <v>-4.354497430838836</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.269685612674988</v>
       </c>
       <c r="E79">
-        <v>-13.20699764079369</v>
+        <v>-14.34375782856914</v>
       </c>
       <c r="F79">
-        <v>-3.530607220639156</v>
+        <v>-2.984887887716273</v>
       </c>
       <c r="G79">
-        <v>-5.178637879567162</v>
+        <v>-3.757831187204912</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.01332891029171</v>
       </c>
       <c r="E80">
-        <v>-14.02309658408601</v>
+        <v>-14.29853648712855</v>
       </c>
       <c r="F80">
-        <v>-3.328375401491504</v>
+        <v>-3.187359933410736</v>
       </c>
       <c r="G80">
-        <v>-4.46699638935435</v>
+        <v>-4.543092589120038</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.734299406989416</v>
       </c>
       <c r="E81">
-        <v>-14.77348736952702</v>
+        <v>-14.38388463675111</v>
       </c>
       <c r="F81">
-        <v>-3.37790431687229</v>
+        <v>-2.80554634501018</v>
       </c>
       <c r="G81">
-        <v>-5.185573472471936</v>
+        <v>-3.631593464701423</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.438708037432934</v>
       </c>
       <c r="E82">
-        <v>-16.27259340502622</v>
+        <v>-16.29918460439926</v>
       </c>
       <c r="F82">
-        <v>-3.591858363136957</v>
+        <v>-3.036067739330838</v>
       </c>
       <c r="G82">
-        <v>-5.004751475116944</v>
+        <v>-3.817914278197144</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.133225031216218</v>
       </c>
       <c r="E83">
-        <v>-16.163833044784</v>
+        <v>-16.76818960042566</v>
       </c>
       <c r="F83">
-        <v>-3.6254552882597</v>
+        <v>-3.153783717473064</v>
       </c>
       <c r="G83">
-        <v>-4.568414951949923</v>
+        <v>-3.358278135524733</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.8232829571300189</v>
       </c>
       <c r="E84">
-        <v>-17.16309970473856</v>
+        <v>-17.56927665238255</v>
       </c>
       <c r="F84">
-        <v>-3.450280433589688</v>
+        <v>-3.184844181608434</v>
       </c>
       <c r="G84">
-        <v>-3.906127074636565</v>
+        <v>-3.078282125449794</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.5151910189925469</v>
       </c>
       <c r="E85">
-        <v>-18.30207884477777</v>
+        <v>-19.35167043637958</v>
       </c>
       <c r="F85">
-        <v>-3.332180092972563</v>
+        <v>-2.975311132172508</v>
       </c>
       <c r="G85">
-        <v>-3.25726677003049</v>
+        <v>-3.558096043184063</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.2180061097867478</v>
       </c>
       <c r="E86">
-        <v>-18.71494434853109</v>
+        <v>-20.42337003808683</v>
       </c>
       <c r="F86">
-        <v>-4.016728832400227</v>
+        <v>-3.177740931129428</v>
       </c>
       <c r="G86">
-        <v>-3.422754320447579</v>
+        <v>-3.137613722604612</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.05886321911510273</v>
       </c>
       <c r="E87">
-        <v>-20.46553465957225</v>
+        <v>-21.48559607217004</v>
       </c>
       <c r="F87">
-        <v>-3.741252767497043</v>
+        <v>-3.141362348268085</v>
       </c>
       <c r="G87">
-        <v>-3.458101015170377</v>
+        <v>-3.059928460980074</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.3045572054019096</v>
       </c>
       <c r="E88">
-        <v>-21.67233675482434</v>
+        <v>-22.38091161127852</v>
       </c>
       <c r="F88">
-        <v>-3.10138202393937</v>
+        <v>-3.284725409568388</v>
       </c>
       <c r="G88">
-        <v>-4.160664989514508</v>
+        <v>-2.745194896561562</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.5032079927739337</v>
       </c>
       <c r="E89">
-        <v>-24.42177257773735</v>
+        <v>-23.46372861667461</v>
       </c>
       <c r="F89">
-        <v>-3.623901271012048</v>
+        <v>-3.143545096374462</v>
       </c>
       <c r="G89">
-        <v>-2.813332544850842</v>
+        <v>-2.97196064491056</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.6418294730605895</v>
       </c>
       <c r="E90">
-        <v>-24.95752728063681</v>
+        <v>-25.44256760312438</v>
       </c>
       <c r="F90">
-        <v>-3.649937686849439</v>
+        <v>-3.120495773391566</v>
       </c>
       <c r="G90">
-        <v>-3.637996059774373</v>
+        <v>-2.422625270851596</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.7106875019807798</v>
       </c>
       <c r="E91">
-        <v>-26.8691320134947</v>
+        <v>-27.01510284465795</v>
       </c>
       <c r="F91">
-        <v>-3.688892492333489</v>
+        <v>-3.087987323036102</v>
       </c>
       <c r="G91">
-        <v>-3.602447421773679</v>
+        <v>-2.743695219432273</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.6972372765814807</v>
       </c>
       <c r="E92">
-        <v>-27.90430947233009</v>
+        <v>-28.90536940799169</v>
       </c>
       <c r="F92">
-        <v>-3.677388954210812</v>
+        <v>-3.045690883449159</v>
       </c>
       <c r="G92">
-        <v>-3.948005475708345</v>
+        <v>-3.031153199152729</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.5935923426653494</v>
       </c>
       <c r="E93">
-        <v>-29.87748333779627</v>
+        <v>-31.93026098360627</v>
       </c>
       <c r="F93">
-        <v>-3.532751863845004</v>
+        <v>-2.871278126789723</v>
       </c>
       <c r="G93">
-        <v>-3.087253703861219</v>
+        <v>-3.48725036864366</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.3995231345752367</v>
       </c>
       <c r="E94">
-        <v>-32.35429596849951</v>
+        <v>-33.60198339132985</v>
       </c>
       <c r="F94">
-        <v>-3.827406290857802</v>
+        <v>-2.926119362324662</v>
       </c>
       <c r="G94">
-        <v>-3.659259693773112</v>
+        <v>-3.213498047455786</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.1145215515060024</v>
       </c>
       <c r="E95">
-        <v>-34.34510144751454</v>
+        <v>-35.2385625765169</v>
       </c>
       <c r="F95">
-        <v>-3.265429419287575</v>
+        <v>-3.290905858760675</v>
       </c>
       <c r="G95">
-        <v>-4.077358421564289</v>
+        <v>-3.798246327148334</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.2633628859390258</v>
       </c>
       <c r="E96">
-        <v>-36.05427886375556</v>
+        <v>-37.17638264540518</v>
       </c>
       <c r="F96">
-        <v>-3.18997094746436</v>
+        <v>-2.965226587410827</v>
       </c>
       <c r="G96">
-        <v>-4.378068515078447</v>
+        <v>-3.803907360020488</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.7173999821765514</v>
       </c>
       <c r="E97">
-        <v>-38.64583170462815</v>
+        <v>-39.70361983418384</v>
       </c>
       <c r="F97">
-        <v>-3.400218877968903</v>
+        <v>-2.891310535691624</v>
       </c>
       <c r="G97">
-        <v>-4.980462002495311</v>
+        <v>-4.429487908394408</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.251885261579569</v>
       </c>
       <c r="E98">
-        <v>-40.53868176238327</v>
+        <v>-41.7083164072174</v>
       </c>
       <c r="F98">
-        <v>-3.449034569015878</v>
+        <v>-2.715274178922701</v>
       </c>
       <c r="G98">
-        <v>-5.201129725960971</v>
+        <v>-4.951445070843599</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.832901459830462</v>
       </c>
       <c r="E99">
-        <v>-43.4710294431771</v>
+        <v>-43.72547986919409</v>
       </c>
       <c r="F99">
-        <v>-3.921019262680772</v>
+        <v>-2.815902594279979</v>
       </c>
       <c r="G99">
-        <v>-4.866595788672078</v>
+        <v>-5.422913103273366</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.477160208005168</v>
       </c>
       <c r="E100">
-        <v>-44.54581519992058</v>
+        <v>-46.27339859876577</v>
       </c>
       <c r="F100">
-        <v>-3.544249603395861</v>
+        <v>-2.814983934830274</v>
       </c>
       <c r="G100">
-        <v>-6.074060994847076</v>
+        <v>-6.042630675497236</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.111778902018148</v>
       </c>
       <c r="E101">
-        <v>-48.01742715096982</v>
+        <v>-48.70429476726824</v>
       </c>
       <c r="F101">
-        <v>-3.236046399142874</v>
+        <v>-2.665948213555601</v>
       </c>
       <c r="G101">
-        <v>-5.91674056027537</v>
+        <v>-6.270296892232915</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.811027243796847</v>
       </c>
       <c r="E102">
-        <v>-50.75650522170879</v>
+        <v>-50.8089415543621</v>
       </c>
       <c r="F102">
-        <v>-2.981499865038823</v>
+        <v>-2.794360071602775</v>
       </c>
       <c r="G102">
-        <v>-6.637161617258331</v>
+        <v>-6.22376386413292</v>
       </c>
     </row>
   </sheetData>
